--- a/hasil_kategorisasi.xlsx
+++ b/hasil_kategorisasi.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Obat &amp; Kesehatan</t>
+          <t>Makanan Instan</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Popok &amp; Pembalut</t>
+          <t>Perawatan Tubuh</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Minuman</t>
+          <t>Frozen Food</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Popok &amp; Pembalut</t>
+          <t>Perawatan Tubuh</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kebersihan Rumah</t>
+          <t>Frozen Food</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ikan &amp; Seafood</t>
+          <t>Bahan Pokok</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Perawatan Tubuh</t>
+          <t>Frozen Food</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kebersihan Rumah</t>
+          <t>Frozen Food</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Perawatan Tubuh</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Minuman</t>
+          <t>Frozen Food</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kebersihan Rumah</t>
+          <t>Frozen Food</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rokok</t>
+          <t>Daging &amp; Olahan</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rokok</t>
+          <t>Daging &amp; Olahan</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rokok</t>
+          <t>Daging &amp; Olahan</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rokok</t>
+          <t>Daging &amp; Olahan</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Frozen Food</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rokok</t>
+          <t>Daging &amp; Olahan</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rokok</t>
+          <t>Snack</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Rokok</t>
+          <t>Frozen Food</t>
         </is>
       </c>
     </row>
